--- a/final_outputs/excel_tables/table_correlation.xlsx
+++ b/final_outputs/excel_tables/table_correlation.xlsx
@@ -475,19 +475,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.042</v>
+        <v>0.061</v>
       </c>
       <c r="D2" t="n">
-        <v>0.021</v>
+        <v>0.099</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.048</v>
+        <v>0.095</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.019</v>
       </c>
     </row>
     <row r="3">
@@ -497,22 +497,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.042</v>
+        <v>0.061</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.179</v>
+        <v>-0.164</v>
       </c>
       <c r="E3" t="n">
-        <v>0.016</v>
+        <v>0.034</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.228</v>
+        <v>-0.195</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.171</v>
+        <v>-0.173</v>
       </c>
     </row>
     <row r="4">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.021</v>
+        <v>0.099</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.179</v>
+        <v>-0.164</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.027</v>
+        <v>-0.006</v>
       </c>
       <c r="F4" t="n">
-        <v>0.145</v>
+        <v>0.161</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.048</v>
+        <v>0.095</v>
       </c>
       <c r="C5" t="n">
-        <v>0.016</v>
+        <v>0.034</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.027</v>
+        <v>-0.006</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.139</v>
+        <v>0.171</v>
       </c>
       <c r="G5" t="n">
-        <v>0.193</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="6">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.228</v>
+        <v>-0.195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.145</v>
+        <v>0.161</v>
       </c>
       <c r="E6" t="n">
-        <v>0.139</v>
+        <v>0.171</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.156</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="7">
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.019</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.171</v>
+        <v>-0.173</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.193</v>
+        <v>0.181</v>
       </c>
       <c r="F7" t="n">
-        <v>0.156</v>
+        <v>0.141</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>

--- a/final_outputs/excel_tables/table_correlation.xlsx
+++ b/final_outputs/excel_tables/table_correlation.xlsx
@@ -475,19 +475,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.061</v>
+        <v>-0.066</v>
       </c>
       <c r="D2" t="n">
-        <v>0.099</v>
+        <v>-0.013</v>
       </c>
       <c r="E2" t="n">
-        <v>0.095</v>
+        <v>-0.118</v>
       </c>
       <c r="F2" t="n">
-        <v>0.122</v>
+        <v>-0.152</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="3">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.061</v>
+        <v>-0.066</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.099</v>
+        <v>-0.013</v>
       </c>
       <c r="C4" t="n">
         <v>-0.164</v>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.095</v>
+        <v>-0.118</v>
       </c>
       <c r="C5" t="n">
         <v>0.034</v>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.122</v>
+        <v>-0.152</v>
       </c>
       <c r="C6" t="n">
         <v>-0.195</v>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.019</v>
+        <v>0.018</v>
       </c>
       <c r="C7" t="n">
         <v>-0.173</v>
